--- a/JsonConverter/ExcelFiles/TileData.xlsx
+++ b/JsonConverter/ExcelFiles/TileData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t xml:space="preserve">타일 ID</t>
   </si>
@@ -49,9 +49,6 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">float</t>
-  </si>
-  <si>
     <t xml:space="preserve">int</t>
   </si>
   <si>
@@ -88,10 +85,58 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_Start_01.prefab</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tile_Exit_01</t>
   </si>
   <si>
     <t xml:space="preserve">Exit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_Exit_01.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_A02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_A02.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_A03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_A03.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_B01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_B01.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_B02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_B02.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_B03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_B03.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile_B04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/03_Prefabs/Environment/Tileset/Tileset01/Tiie_B04.prefab</t>
   </si>
 </sst>
 </file>
@@ -101,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -124,6 +169,13 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="129"/>
     </font>
@@ -176,12 +228,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -368,145 +428,307 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="19.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="64.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="21.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="59.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="19.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="21.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="64.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="21.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="59.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="true" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="2" customFormat="true" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="0"/>
-    </row>
-    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="0" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>1</v>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
